--- a/data/cloud/content/allocation_norms/ncf_chapterwise_period_allocation.xlsx
+++ b/data/cloud/content/allocation_norms/ncf_chapterwise_period_allocation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10809"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10823"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kumar_radhakrishnan/main/kumar/AI/aruvi-saas/data/content/allocation_norms/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kumar_radhakrishnan/main/kumar/AI/aruvi-saas/data/cloud/content/allocation_norms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7778DBB2-81AF-7A49-A33D-98799EBD4F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7A1361-6E12-3A40-A1AB-97702CAB4BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="16380" windowHeight="17400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28020" windowHeight="17400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="budget" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">budget!$A$1:$C$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">budget!$A$1:$D$41</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1480" uniqueCount="703">
   <si>
     <t>Chapter-wise Period Allocation</t>
   </si>
@@ -2137,6 +2137,15 @@
   </si>
   <si>
     <t>X</t>
+  </si>
+  <si>
+    <t>NCF</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>NCF- English computed as NCF English + 50% of third language NCF budget</t>
   </si>
 </sst>
 </file>
@@ -2146,7 +2155,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.####"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2236,6 +2245,41 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2337,7 +2381,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2397,6 +2441,27 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2660,6 +2725,28 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{0C55DCED-9CA4-424B-A924-C7EBA0D7ECAE}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;8856aa81-b929-4f1f-b0ef-78db28c0d800&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H28"/>
@@ -2703,7 +2790,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>7</v>
@@ -2757,15 +2844,15 @@
       </c>
       <c r="B10" s="10" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Family and Friends</v>
+        <v>Water — The Essence of Life</v>
       </c>
       <c r="C10" s="11">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="D10" s="12">
         <f>IF(OR($C10="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C10)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C10)-$C10)/$C$28*$B$6,0))</f>
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2775,15 +2862,15 @@
       </c>
       <c r="B11" s="10" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Going to the Mela</v>
+        <v>Journey of a River</v>
       </c>
       <c r="C11" s="11">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="D11" s="12">
         <f>IF(OR($C11="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C11)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C11)-$C11)/$C$28*$B$6,0))</f>
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2793,7 +2880,7 @@
       </c>
       <c r="B12" s="10" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Celebrating Festivals</v>
+        <v>The Mystery of Food</v>
       </c>
       <c r="C12" s="11">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
@@ -2801,7 +2888,7 @@
       </c>
       <c r="D12" s="12">
         <f>IF(OR($C12="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C12)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C12)-$C12)/$C$28*$B$6,0))</f>
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2811,15 +2898,15 @@
       </c>
       <c r="B13" s="10" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Getting to Know Plants</v>
+        <v>Our School—A Happy Place</v>
       </c>
       <c r="C13" s="11">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="D13" s="12">
         <f>IF(OR($C13="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C13)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C13)-$C13)/$C$28*$B$6,0))</f>
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2829,15 +2916,15 @@
       </c>
       <c r="B14" s="10" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Plants and Animals Live Together</v>
+        <v>Our Vibrant Country</v>
       </c>
       <c r="C14" s="11">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D14" s="12">
         <f>IF(OR($C14="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C14)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C14)-$C14)/$C$28*$B$6,0))</f>
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2847,15 +2934,15 @@
       </c>
       <c r="B15" s="10" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Living in Harmony</v>
+        <v>Some Unique Places</v>
       </c>
       <c r="C15" s="11">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="D15" s="12">
         <f>IF(OR($C15="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C15)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C15)-$C15)/$C$28*$B$6,0))</f>
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2865,15 +2952,15 @@
       </c>
       <c r="B16" s="10" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Water–A Precious Gift</v>
+        <v>Energy—How Things Work</v>
       </c>
       <c r="C16" s="11">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="D16" s="12">
         <f>IF(OR($C16="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C16)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C16)-$C16)/$C$28*$B$6,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2883,15 +2970,15 @@
       </c>
       <c r="B17" s="10" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Food We Eat</v>
+        <v>Clothes—How Things are Made</v>
       </c>
       <c r="C17" s="11">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D17" s="12">
         <f>IF(OR($C17="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C17)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C17)-$C17)/$C$28*$B$6,0))</f>
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2901,15 +2988,15 @@
       </c>
       <c r="B18" s="10" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Staying Healthy and Happy</v>
+        <v>Rhythms of Nature</v>
       </c>
       <c r="C18" s="11">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>3.5</v>
+        <v>9.5</v>
       </c>
       <c r="D18" s="12">
         <f>IF(OR($C18="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C18)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C18)-$C18)/$C$28*$B$6,0))</f>
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2919,51 +3006,51 @@
       </c>
       <c r="B19" s="10" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>This World of Things</v>
+        <v>Earth—Our Shared Home</v>
       </c>
       <c r="C19" s="11">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="D19" s="12">
         <f>IF(OR($C19="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C19)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C19)-$C19)/$C$28*$B$6,0))</f>
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="9">
+      <c r="A20" s="9" t="str">
         <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>11</v>
+        <v/>
       </c>
       <c r="B20" s="10" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Making Things</v>
-      </c>
-      <c r="C20" s="11">
+        <v/>
+      </c>
+      <c r="C20" s="11" t="str">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>9.5</v>
-      </c>
-      <c r="D20" s="12">
+        <v/>
+      </c>
+      <c r="D20" s="12" t="str">
         <f>IF(OR($C20="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C20)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C20)-$C20)/$C$28*$B$6,0))</f>
-        <v>17</v>
+        <v/>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="9">
+      <c r="A21" s="9" t="str">
         <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>12</v>
+        <v/>
       </c>
       <c r="B21" s="10" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Taking Charge of Waste</v>
-      </c>
-      <c r="C21" s="11">
+        <v/>
+      </c>
+      <c r="C21" s="11" t="str">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>9.5</v>
-      </c>
-      <c r="D21" s="12">
+        <v/>
+      </c>
+      <c r="D21" s="12" t="str">
         <f>IF(OR($C21="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C21)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C21)-$C21)/$C$28*$B$6,0))</f>
-        <v>16</v>
+        <v/>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3080,7 +3167,7 @@
       </c>
       <c r="C28" s="14">
         <f>SUM(C10:C27)</f>
-        <v>81.5</v>
+        <v>107</v>
       </c>
       <c r="D28" s="15">
         <f>SUM(D10:D27)</f>
@@ -10977,15 +11064,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="16" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>2</v>
       </c>
@@ -10995,8 +11085,12 @@
       <c r="C1" s="17" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D1" s="36" t="s">
+        <v>700</v>
+      </c>
+      <c r="F1" s="29"/>
+    </row>
+    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
         <v>3</v>
       </c>
@@ -11006,8 +11100,14 @@
       <c r="C2" s="21">
         <v>160</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D2" s="33">
+        <v>126</v>
+      </c>
+      <c r="F2" s="35" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="19" t="s">
         <v>227</v>
       </c>
@@ -11017,8 +11117,11 @@
       <c r="C3" s="21">
         <v>210</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D3" s="33">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="19" t="s">
         <v>421</v>
       </c>
@@ -11028,8 +11131,11 @@
       <c r="C4" s="21">
         <v>210</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D4" s="33">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
         <v>634</v>
       </c>
@@ -11037,8 +11143,13 @@
         <v>194</v>
       </c>
       <c r="C5" s="21"/>
-    </row>
-    <row r="6" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D5" s="33" t="s">
+        <v>701</v>
+      </c>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+    </row>
+    <row r="6" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="19" t="s">
         <v>522</v>
       </c>
@@ -11048,8 +11159,11 @@
       <c r="C6" s="21">
         <v>245</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D6" s="33">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
         <v>3</v>
       </c>
@@ -11059,8 +11173,11 @@
       <c r="C7" s="21">
         <v>140</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D7" s="33">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
         <v>227</v>
       </c>
@@ -11070,8 +11187,12 @@
       <c r="C8" s="21">
         <v>180</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D8" s="33">
+        <v>172</v>
+      </c>
+      <c r="F8" s="29"/>
+    </row>
+    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
         <v>421</v>
       </c>
@@ -11081,8 +11202,12 @@
       <c r="C9" s="21">
         <v>180</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D9" s="33">
+        <v>240</v>
+      </c>
+      <c r="G9" s="31"/>
+    </row>
+    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="19" t="s">
         <v>634</v>
       </c>
@@ -11090,8 +11215,12 @@
         <v>99</v>
       </c>
       <c r="C10" s="21"/>
-    </row>
-    <row r="11" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D10" s="33" t="s">
+        <v>701</v>
+      </c>
+      <c r="G10" s="31"/>
+    </row>
+    <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
         <v>522</v>
       </c>
@@ -11101,8 +11230,11 @@
       <c r="C11" s="21">
         <v>210</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D11" s="33">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
         <v>3</v>
       </c>
@@ -11112,8 +11244,11 @@
       <c r="C12" s="21">
         <v>140</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D12" s="33">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
         <v>227</v>
       </c>
@@ -11123,8 +11258,12 @@
       <c r="C13" s="21">
         <v>160</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D13" s="33">
+        <v>277</v>
+      </c>
+      <c r="G13" s="32"/>
+    </row>
+    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
         <v>421</v>
       </c>
@@ -11132,8 +11271,12 @@
         <v>6</v>
       </c>
       <c r="C14" s="21"/>
-    </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D14" s="33" t="s">
+        <v>701</v>
+      </c>
+      <c r="G14" s="31"/>
+    </row>
+    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="19" t="s">
         <v>634</v>
       </c>
@@ -11143,8 +11286,12 @@
       <c r="C15" s="21">
         <v>140</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D15" s="33">
+        <v>300</v>
+      </c>
+      <c r="G15" s="31"/>
+    </row>
+    <row r="16" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="19" t="s">
         <v>522</v>
       </c>
@@ -11152,8 +11299,11 @@
         <v>6</v>
       </c>
       <c r="C16" s="21"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D16" s="33" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="19" t="s">
         <v>3</v>
       </c>
@@ -11163,8 +11313,11 @@
       <c r="C17" s="21">
         <v>160</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D17" s="33">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="19" t="s">
         <v>227</v>
       </c>
@@ -11174,8 +11327,13 @@
       <c r="C18" s="21">
         <v>210</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D18" s="33">
+        <v>162</v>
+      </c>
+      <c r="F18" s="28"/>
+      <c r="G18" s="34"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="19" t="s">
         <v>421</v>
       </c>
@@ -11185,8 +11343,11 @@
       <c r="C19" s="21">
         <v>210</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D19" s="33">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="19" t="s">
         <v>634</v>
       </c>
@@ -11194,8 +11355,11 @@
         <v>699</v>
       </c>
       <c r="C20" s="21"/>
-    </row>
-    <row r="21" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D20" s="33" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="19" t="s">
         <v>522</v>
       </c>
@@ -11205,8 +11369,11 @@
       <c r="C21" s="21">
         <v>245</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D21" s="33">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="19" t="s">
         <v>3</v>
       </c>
@@ -11216,8 +11383,11 @@
       <c r="C22" s="21">
         <v>140</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D22" s="33">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="19" t="s">
         <v>227</v>
       </c>
@@ -11227,8 +11397,11 @@
       <c r="C23" s="21">
         <v>180</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D23" s="33">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="19" t="s">
         <v>421</v>
       </c>
@@ -11238,8 +11411,11 @@
       <c r="C24" s="21">
         <v>180</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D24" s="33">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="19" t="s">
         <v>634</v>
       </c>
@@ -11247,8 +11423,11 @@
         <v>132</v>
       </c>
       <c r="C25" s="21"/>
-    </row>
-    <row r="26" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D25" s="33" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="19" t="s">
         <v>522</v>
       </c>
@@ -11258,8 +11437,11 @@
       <c r="C26" s="21">
         <v>210</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D26" s="33">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="19" t="s">
         <v>3</v>
       </c>
@@ -11269,8 +11451,12 @@
       <c r="C27" s="21">
         <v>140</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D27" s="33">
+        <v>270</v>
+      </c>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="19" t="s">
         <v>227</v>
       </c>
@@ -11280,8 +11466,11 @@
       <c r="C28" s="21">
         <v>160</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D28" s="33">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="19" t="s">
         <v>421</v>
       </c>
@@ -11289,8 +11478,11 @@
         <v>53</v>
       </c>
       <c r="C29" s="21"/>
-    </row>
-    <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D29" s="33" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="19" t="s">
         <v>634</v>
       </c>
@@ -11300,8 +11492,11 @@
       <c r="C30" s="21">
         <v>140</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D30" s="33">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="19" t="s">
         <v>522</v>
       </c>
@@ -11309,8 +11504,11 @@
         <v>53</v>
       </c>
       <c r="C31" s="21"/>
-    </row>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D31" s="33" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="19" t="s">
         <v>3</v>
       </c>
@@ -11320,8 +11518,11 @@
       <c r="C32" s="21">
         <v>140</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D32" s="33">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="19" t="s">
         <v>227</v>
       </c>
@@ -11331,8 +11532,11 @@
       <c r="C33" s="21">
         <v>160</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D33" s="33">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="19" t="s">
         <v>421</v>
       </c>
@@ -11340,8 +11544,11 @@
         <v>78</v>
       </c>
       <c r="C34" s="21"/>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D34" s="33" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="19" t="s">
         <v>634</v>
       </c>
@@ -11351,8 +11558,11 @@
       <c r="C35" s="21">
         <v>140</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D35" s="33">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="19" t="s">
         <v>522</v>
       </c>
@@ -11360,8 +11570,11 @@
         <v>78</v>
       </c>
       <c r="C36" s="21"/>
-    </row>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D36" s="33" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="23" t="s">
         <v>3</v>
       </c>
@@ -11371,8 +11584,11 @@
       <c r="C37" s="21">
         <v>140</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D37" s="33">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="19" t="s">
         <v>227</v>
       </c>
@@ -11382,8 +11598,11 @@
       <c r="C38" s="21">
         <v>180</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D38" s="33">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="23" t="s">
         <v>421</v>
       </c>
@@ -11393,8 +11612,11 @@
       <c r="C39" s="21">
         <v>180</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D39" s="33">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="19" t="s">
         <v>634</v>
       </c>
@@ -11402,8 +11624,11 @@
         <v>163</v>
       </c>
       <c r="C40" s="21"/>
-    </row>
-    <row r="41" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D40" s="33" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="23" t="s">
         <v>522</v>
       </c>
@@ -11413,14 +11638,17 @@
       <c r="C41" s="21">
         <v>210</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="D41" s="33">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <autoFilter ref="A1:C46" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:D41" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
